--- a/inst/extdata/ex02/User_21062019.xlsx
+++ b/inst/extdata/ex02/User_21062019.xlsx
@@ -5,11 +5,11 @@
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Profils\mcanouil\Downloads\DATA\endoc_beta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Profils\mcanouil\Downloads\DATA\endoc_beta\ex02\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11400" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11400" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Blank" sheetId="3" r:id="rId1"/>
@@ -52,12 +52,6 @@
     <t>BLANK</t>
   </si>
   <si>
-    <t>SN1</t>
-  </si>
-  <si>
-    <t>SN2</t>
-  </si>
-  <si>
     <t>Sample</t>
   </si>
   <si>
@@ -92,9 +86,6 @@
   </si>
   <si>
     <t>Concentration (µg/L)</t>
-  </si>
-  <si>
-    <t>LYSAT</t>
   </si>
   <si>
     <t>Target</t>
@@ -140,6 +131,15 @@
   </si>
   <si>
     <t>0.5 mM Glc + A</t>
+  </si>
+  <si>
+    <t>LYSATE</t>
+  </si>
+  <si>
+    <t>SUPERNATANT1</t>
+  </si>
+  <si>
+    <t>SUPERNATANT2</t>
   </si>
 </sst>
 </file>
@@ -3605,13 +3605,13 @@
         <v>3</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>9</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>1</v>
@@ -3620,19 +3620,19 @@
         <v>0</v>
       </c>
       <c r="H1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I1" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="N1" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
@@ -3640,10 +3640,10 @@
         <v>43637</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>4</v>
@@ -3895,22 +3895,22 @@
         <v>3</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>20</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>23</v>
       </c>
       <c r="I1" s="3" t="s">
         <v>1</v>
@@ -3919,19 +3919,19 @@
         <v>0</v>
       </c>
       <c r="K1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
@@ -3952,16 +3952,16 @@
         <v>CT</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I2" s="1">
         <v>0.72577979999999997</v>
@@ -4004,16 +4004,16 @@
         <v>CT</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I3" s="1">
         <v>0.65571389999999996</v>
@@ -4056,16 +4056,16 @@
         <v>CT</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I4" s="1">
         <v>0.50042019999999998</v>
@@ -4108,16 +4108,16 @@
         <v>CT</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I5" s="1">
         <v>0.453345</v>
@@ -4160,16 +4160,16 @@
         <v>CT</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I6" s="1">
         <v>0.56810300000000002</v>
@@ -4212,16 +4212,16 @@
         <v>CT</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I7" s="1">
         <v>0.49746119999999999</v>
@@ -4264,16 +4264,16 @@
         <v>CT</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="F8" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G8" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H8" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I8">
         <v>0.21018310000000001</v>
@@ -4318,16 +4318,16 @@
         <v>CT</v>
       </c>
       <c r="E9" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="F9" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G9" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H9" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I9">
         <v>0.2101151</v>
@@ -4372,16 +4372,16 @@
         <v>CT</v>
       </c>
       <c r="E10" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="F10" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G10" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H10" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I10">
         <v>0.21359049999999999</v>
@@ -4426,16 +4426,16 @@
         <v>CT</v>
       </c>
       <c r="E11" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="F11" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G11" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I11">
         <v>0.25941049999999999</v>
@@ -4480,16 +4480,16 @@
         <v>CT</v>
       </c>
       <c r="E12" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="F12" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G12" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H12" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I12">
         <v>0.25336170000000002</v>
@@ -4534,16 +4534,16 @@
         <v>CT</v>
       </c>
       <c r="E13" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="F13" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G13" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H13" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I13">
         <v>0.2765396</v>
@@ -4588,16 +4588,16 @@
         <v>CT</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I14" s="1">
         <v>0.26221440000000001</v>
@@ -4642,16 +4642,16 @@
         <v>CT</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I15" s="1">
         <v>0.28478989999999998</v>
@@ -4696,16 +4696,16 @@
         <v>CT</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I16" s="1">
         <v>0.28484660000000001</v>
@@ -4750,16 +4750,16 @@
         <v>CT</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I17" s="1">
         <v>0.4396661</v>
@@ -4804,16 +4804,16 @@
         <v>CT</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I18" s="1">
         <v>0.40413450000000001</v>
@@ -4858,16 +4858,16 @@
         <v>CT</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I19" s="1">
         <v>0.46948699999999999</v>
@@ -4927,22 +4927,22 @@
         <v>3</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>20</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>23</v>
       </c>
       <c r="I1" s="3" t="s">
         <v>1</v>
@@ -4951,19 +4951,19 @@
         <v>0</v>
       </c>
       <c r="K1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
@@ -4984,16 +4984,16 @@
         <v>Empty</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="H2" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I2" s="1">
         <v>0.31487480000000001</v>
@@ -5036,17 +5036,17 @@
         <v>Empty</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F3" s="1" t="str">
         <f>$F$2</f>
         <v>Control</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I3" s="1">
         <v>0.28390149999999997</v>
@@ -5089,17 +5089,17 @@
         <v>Empty</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F4" s="1" t="str">
         <f t="shared" ref="F4:F19" si="2">$F$2</f>
         <v>Control</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I4" s="1">
         <v>0.28726489999999999</v>
@@ -5142,17 +5142,17 @@
         <v>Empty</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F5" s="1" t="str">
         <f t="shared" si="2"/>
         <v>Control</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I5" s="1">
         <v>0.27028449999999998</v>
@@ -5195,17 +5195,17 @@
         <v>Empty</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F6" s="1" t="str">
         <f t="shared" si="2"/>
         <v>Control</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I6" s="1">
         <v>0.2455475</v>
@@ -5248,17 +5248,17 @@
         <v>Empty</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F7" s="1" t="str">
         <f t="shared" si="2"/>
         <v>Control</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I7" s="1">
         <v>0.25412760000000001</v>
@@ -5301,17 +5301,17 @@
         <v>Empty</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="F8" s="4" t="str">
         <f t="shared" si="2"/>
         <v>Control</v>
       </c>
       <c r="G8" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H8" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I8">
         <v>0.19914000000000001</v>
@@ -5356,17 +5356,17 @@
         <v>Empty</v>
       </c>
       <c r="E9" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="F9" s="4" t="str">
         <f t="shared" si="2"/>
         <v>Control</v>
       </c>
       <c r="G9" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H9" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I9">
         <v>0.21093780000000001</v>
@@ -5411,17 +5411,17 @@
         <v>Empty</v>
       </c>
       <c r="E10" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="F10" s="4" t="str">
         <f t="shared" si="2"/>
         <v>Control</v>
       </c>
       <c r="G10" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H10" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I10">
         <v>0.20028979999999999</v>
@@ -5466,17 +5466,17 @@
         <v>Empty</v>
       </c>
       <c r="E11" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="F11" s="4" t="str">
         <f t="shared" si="2"/>
         <v>Control</v>
       </c>
       <c r="G11" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I11">
         <v>0.2320488</v>
@@ -5521,17 +5521,17 @@
         <v>Empty</v>
       </c>
       <c r="E12" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="F12" s="4" t="str">
         <f t="shared" si="2"/>
         <v>Control</v>
       </c>
       <c r="G12" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H12" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I12">
         <v>0.2405775</v>
@@ -5576,17 +5576,17 @@
         <v>Empty</v>
       </c>
       <c r="E13" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="F13" s="4" t="str">
         <f t="shared" si="2"/>
         <v>Control</v>
       </c>
       <c r="G13" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H13" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I13">
         <v>0.24642539999999999</v>
@@ -5631,17 +5631,17 @@
         <v>Empty</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="F14" s="1" t="str">
         <f t="shared" si="2"/>
         <v>Control</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I14" s="1">
         <v>0.24015600000000001</v>
@@ -5686,17 +5686,17 @@
         <v>Empty</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="F15" s="1" t="str">
         <f t="shared" si="2"/>
         <v>Control</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I15" s="1">
         <v>0.25050410000000001</v>
@@ -5741,17 +5741,17 @@
         <v>Empty</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="F16" s="1" t="str">
         <f t="shared" si="2"/>
         <v>Control</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I16" s="1">
         <v>0.24917810000000001</v>
@@ -5796,17 +5796,17 @@
         <v>Empty</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="F17" s="1" t="str">
         <f t="shared" si="2"/>
         <v>Control</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I17" s="1">
         <v>0.30625089999999999</v>
@@ -5851,17 +5851,17 @@
         <v>Empty</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="F18" s="1" t="str">
         <f t="shared" si="2"/>
         <v>Control</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I18" s="1">
         <v>0.32483089999999998</v>
@@ -5906,17 +5906,17 @@
         <v>Empty</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="F19" s="1" t="str">
         <f t="shared" si="2"/>
         <v>Control</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I19" s="1">
         <v>0.32798959999999999</v>
@@ -5976,22 +5976,22 @@
         <v>3</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>20</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>23</v>
       </c>
       <c r="I1" s="3" t="s">
         <v>1</v>
@@ -6000,19 +6000,19 @@
         <v>0</v>
       </c>
       <c r="K1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
@@ -6033,16 +6033,16 @@
         <v>GENE</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I2" s="1">
         <v>0.33028550000000001</v>
@@ -6085,16 +6085,16 @@
         <v>GENE</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I3" s="1">
         <v>0.31443280000000001</v>
@@ -6137,16 +6137,16 @@
         <v>GENE</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I4" s="1">
         <v>0.28509699999999999</v>
@@ -6189,16 +6189,16 @@
         <v>GENE</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I5" s="1">
         <v>0.27847379999999999</v>
@@ -6241,16 +6241,16 @@
         <v>GENE</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I6" s="1">
         <v>0.29445959999999999</v>
@@ -6293,16 +6293,16 @@
         <v>GENE</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I7" s="1">
         <v>0.24770439999999999</v>
@@ -6345,16 +6345,16 @@
         <v>GENE</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="F8" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G8" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H8" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I8">
         <v>0.18238860000000001</v>
@@ -6399,16 +6399,16 @@
         <v>GENE</v>
       </c>
       <c r="E9" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="F9" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G9" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H9" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I9">
         <v>0.18535570000000001</v>
@@ -6453,16 +6453,16 @@
         <v>GENE</v>
       </c>
       <c r="E10" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="F10" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G10" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H10" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I10">
         <v>0.20159450000000001</v>
@@ -6507,16 +6507,16 @@
         <v>GENE</v>
       </c>
       <c r="E11" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="F11" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G11" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I11">
         <v>0.22433120000000001</v>
@@ -6561,16 +6561,16 @@
         <v>GENE</v>
       </c>
       <c r="E12" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="F12" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G12" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H12" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I12">
         <v>0.21561959999999999</v>
@@ -6615,16 +6615,16 @@
         <v>GENE</v>
       </c>
       <c r="E13" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="F13" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G13" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H13" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I13">
         <v>0.22002849999999999</v>
@@ -6669,16 +6669,16 @@
         <v>GENE</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I14" s="1">
         <v>0.20931420000000001</v>
@@ -6723,16 +6723,16 @@
         <v>GENE</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I15" s="1">
         <v>0.20966599999999999</v>
@@ -6777,16 +6777,16 @@
         <v>GENE</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I16" s="1">
         <v>0.2084114</v>
@@ -6831,16 +6831,16 @@
         <v>GENE</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I17" s="1">
         <v>0.29100890000000001</v>
@@ -6885,16 +6885,16 @@
         <v>GENE</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I18" s="1">
         <v>0.37590859999999998</v>
@@ -6939,16 +6939,16 @@
         <v>GENE</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I19" s="1">
         <v>0.31013740000000001</v>
